--- a/SensWear-V1R2-Debug/Output/Manufacturing/Assembly/Bill of Materials/Bill of Materials-SensWear-V1R2-Debug.xlsx
+++ b/SensWear-V1R2-Debug/Output/Manufacturing/Assembly/Bill of Materials/Bill of Materials-SensWear-V1R2-Debug.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salamid1\Desktop\Projects\SenseWear\Hardware\hardware-v1\SensWear-V1R2-Debug\Output\Manufacturing\Assembly\Bill of Materials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORK\Projects\SensWear\hardware-v1\SensWear-V1R2-Debug\Output\Manufacturing\Assembly\Bill of Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFFE50A0-F908-4FA1-B9B8-9C0191B37854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CBEDD3-465B-40B0-B643-85F6CACE36E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{B439749A-5F0D-44B8-A094-09FAD062DDD9}"/>
+    <workbookView xWindow="3790" yWindow="3660" windowWidth="28800" windowHeight="17170" xr2:uid="{8B973B5F-F8C3-4C86-81CB-9745F1413E71}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-SensWear-V1R2" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="171">
+  <si>
+    <t>Manufacturer</t>
+  </si>
   <si>
     <t>Manufacturer Part Number</t>
   </si>
@@ -62,12 +65,30 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Footprint</t>
+  </si>
+  <si>
     <t>Supplier 1</t>
   </si>
   <si>
     <t>Supplier Part Number 1</t>
   </si>
   <si>
+    <t>U53</t>
+  </si>
+  <si>
+    <t>RP2354A</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>QFN40P700X700X90_HS-61N</t>
+  </si>
+  <si>
+    <t>JST</t>
+  </si>
+  <si>
     <t>SWD_RP50, UART_RP50</t>
   </si>
   <si>
@@ -77,19 +98,16 @@
     <t>Male Header, Pitch 1 mm, 1 x 3 Position, Height 2.9 mm, -25 to 85 degC, RoHS, Tape and Reel</t>
   </si>
   <si>
+    <t>JST-SM03B-SRSS-TB_V</t>
+  </si>
+  <si>
     <t>Mouser</t>
   </si>
   <si>
     <t>306-SM03BSRSSTBLFSNP</t>
   </si>
   <si>
-    <t>U53</t>
-  </si>
-  <si>
-    <t>RP2354A</t>
-  </si>
-  <si>
-    <t/>
+    <t>Molex</t>
   </si>
   <si>
     <t>504754-1100</t>
@@ -101,6 +119,9 @@
     <t>Conn FFC/FPC Connector SKT 11 POS 0.3mm Solder RA SMD Easy-On™ T/R</t>
   </si>
   <si>
+    <t>5047541100__3</t>
+  </si>
+  <si>
     <t>538-504754-1100</t>
   </si>
   <si>
@@ -116,6 +137,9 @@
     <t>538-15031-0411</t>
   </si>
   <si>
+    <t>Abracon</t>
+  </si>
+  <si>
     <t>ABM8-272-T3</t>
   </si>
   <si>
@@ -128,6 +152,9 @@
     <t>Parallel - Fundamental Quartz Crystal, 12MHz Nom</t>
   </si>
   <si>
+    <t>DFN165P250X80-4N</t>
+  </si>
+  <si>
     <t>DigiKey</t>
   </si>
   <si>
@@ -146,6 +173,12 @@
     <t>General Purpose Inductor, 3.3uH, 20%, 1 Element, SMD, 0806</t>
   </si>
   <si>
+    <t>AOTAB201610S3R3101T</t>
+  </si>
+  <si>
+    <t>Omron Electronics Inc-EMC Div</t>
+  </si>
+  <si>
     <t>B3U-1000P</t>
   </si>
   <si>
@@ -161,6 +194,9 @@
     <t>SW1020DKR-ND</t>
   </si>
   <si>
+    <t>Murata</t>
+  </si>
+  <si>
     <t>BLM15AG601SN1D</t>
   </si>
   <si>
@@ -170,9 +206,15 @@
     <t>FERRITE BEAD 600 OHM 0402 1LN</t>
   </si>
   <si>
+    <t>MURA-BLM15-CHIP-2_V</t>
+  </si>
+  <si>
     <t>490-1006-1-ND</t>
   </si>
   <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
     <t>CSD87502Q2</t>
   </si>
   <si>
@@ -182,6 +224,9 @@
     <t>Transistor MOSFET Array Dual N-CH 30V 5A 6-Pin WSON T/R</t>
   </si>
   <si>
+    <t>FP-DQK0006B-MFG</t>
+  </si>
+  <si>
     <t>296-48123-1-ND</t>
   </si>
   <si>
@@ -197,9 +242,15 @@
     <t>Inductor Power Shielded Wirewound 2.2uH 20% 1MHz Metal 1.8A 0.116Ohm DCR 0806 T/R</t>
   </si>
   <si>
+    <t>FP-DFE201612C-MFG</t>
+  </si>
+  <si>
     <t>81-DFE201612E-2R2MP2</t>
   </si>
   <si>
+    <t>JAE Electronics</t>
+  </si>
+  <si>
     <t>DX07S024JJ3R1300</t>
   </si>
   <si>
@@ -209,9 +260,15 @@
     <t>Cut Tape - Usb Type C Receptacle Mid Mnt Dual R</t>
   </si>
   <si>
+    <t>JAE-DX07S024JJ3R1300-MFG</t>
+  </si>
+  <si>
     <t>656-DX07S024JJ3R1300</t>
   </si>
   <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
     <t>ERJ-2RKF27R0X</t>
   </si>
   <si>
@@ -224,6 +281,9 @@
     <t>Res Thick Film 0402 27 Ohm 1% 0.1W ±100ppm/°C Molded SMD Punched Carrier T/R</t>
   </si>
   <si>
+    <t>RESC1005X04N</t>
+  </si>
+  <si>
     <t>ERJ-2RKF33R0X</t>
   </si>
   <si>
@@ -239,6 +299,9 @@
     <t>667-ERJ-2RKF33R0X</t>
   </si>
   <si>
+    <t>Panasonic Electronic Components</t>
+  </si>
+  <si>
     <t>ERJ-2RKF1000X</t>
   </si>
   <si>
@@ -326,6 +389,9 @@
     <t>P620LCT-ND</t>
   </si>
   <si>
+    <t>Fairchild Semiconductor</t>
+  </si>
+  <si>
     <t>FPF1320UCX</t>
   </si>
   <si>
@@ -335,9 +401,15 @@
     <t>IC ADVANCED POWER SWITCH 6WLCSP</t>
   </si>
   <si>
+    <t>BGA6C50P2X3_96X146X62</t>
+  </si>
+  <si>
     <t>FPF1320UCXDKR-ND</t>
   </si>
   <si>
+    <t>Murata Electronics North America</t>
+  </si>
+  <si>
     <t>GRM155R61A104KA01D</t>
   </si>
   <si>
@@ -350,6 +422,9 @@
     <t>CAP CER 0.1UF 10V X5R 0402</t>
   </si>
   <si>
+    <t>CAPC1005X05N</t>
+  </si>
+  <si>
     <t>490-1318-6-ND</t>
   </si>
   <si>
@@ -380,6 +455,9 @@
     <t>CAP CER 4.7UF 10V X5R 0603</t>
   </si>
   <si>
+    <t>CAPC1610X05N</t>
+  </si>
+  <si>
     <t>490-10477-6-ND</t>
   </si>
   <si>
@@ -395,6 +473,9 @@
     <t>CAP CER 15 pF 25V C0G 0402</t>
   </si>
   <si>
+    <t>Vishay Lite-On</t>
+  </si>
+  <si>
     <t>LTST-C155KGJRKT</t>
   </si>
   <si>
@@ -407,6 +488,9 @@
     <t>160-1409-1-ND</t>
   </si>
   <si>
+    <t>ON Semiconductor</t>
+  </si>
+  <si>
     <t>MBR140SFT1G</t>
   </si>
   <si>
@@ -416,9 +500,15 @@
     <t>DIODE SCHOTTKY 40V 1A SOD123L</t>
   </si>
   <si>
+    <t>SODFL360X110-2N</t>
+  </si>
+  <si>
     <t>MBR140SFT1GOSDKR-ND</t>
   </si>
   <si>
+    <t>NXP Semiconductors</t>
+  </si>
+  <si>
     <t>PRTR5V0U2F,115</t>
   </si>
   <si>
@@ -431,6 +521,9 @@
     <t>TVS DIODE 5.5VWM SOT886</t>
   </si>
   <si>
+    <t>SON50P100X50-6N</t>
+  </si>
+  <si>
     <t>568-4677-6-ND</t>
   </si>
   <si>
@@ -443,6 +536,9 @@
     <t>Schmitt Trigger 32mA 1 1.65V~5.5V 32mA 1 BGA-5 Buffer/Driver/Transceiver ROHS</t>
   </si>
   <si>
+    <t>YZP0005ADAD</t>
+  </si>
+  <si>
     <t>296-SN74LVC1G17YZPRCT-ND</t>
   </si>
   <si>
@@ -453,6 +549,9 @@
   </si>
   <si>
     <t>Conv DC-DC 1.8V to 6.5V Synchronous Step Down Single-Out 1.8V to 3.3V 0.75A 6-Pin DSBGA T/R</t>
+  </si>
+  <si>
+    <t>BGA6C40P2X3_97X147X50</t>
   </si>
   <si>
     <t>595-TPS62840YBGR</t>
@@ -851,21 +950,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E11163-8244-452E-9B73-24ED490E3416}">
-  <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{565210E0-A35A-4564-BC25-453C35CDFA05}">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.796875" customWidth="1"/>
-    <col min="2" max="2" width="29.1328125" customWidth="1"/>
-    <col min="3" max="3" width="9.265625" customWidth="1"/>
-    <col min="4" max="4" width="15.53125" customWidth="1"/>
-    <col min="5" max="5" width="23.9296875" customWidth="1"/>
-    <col min="6" max="6" width="99.265625" customWidth="1"/>
-    <col min="7" max="7" width="17.796875" customWidth="1"/>
-    <col min="8" max="8" width="25.3984375" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="3" max="3" width="29.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="24.26953125" customWidth="1"/>
+    <col min="7" max="7" width="100.7265625" customWidth="1"/>
+    <col min="8" max="8" width="15.81640625" customWidth="1"/>
+    <col min="9" max="9" width="18.08984375" customWidth="1"/>
+    <col min="10" max="10" width="25.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -890,709 +991,887 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="2" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="1">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="E16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="1">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="1">
+        <v>101</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+        <v>103</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="1">
+        <v>105</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="1">
         <v>2</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="1">
+        <v>110</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="1">
         <v>6</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="1">
+        <v>14</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="1">
+        <v>6</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="J28" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="1">
         <v>1</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="1">
-        <v>14</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="1">
-        <v>6</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C25" s="1">
-        <v>2</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A26" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="1">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A28" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A29" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="1">
-        <v>2</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="E30" s="1"/>
       <c r="F30" s="2" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>137</v>
+        <v>169</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>